--- a/daily_matches/job_matches_2026-05-17.xlsx
+++ b/daily_matches/job_matches_2026-05-17.xlsx
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Linux Systems Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,34 +486,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b4ec4ddf5614d5</t>
+          <t>https://www.indeed.com/viewjob?jk=97dd13894809f36a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - PhD or PhD Candidate (Near Completion)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optimal Inc.</t>
+          <t>KT2i Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,34 +521,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, Docker, Git, Python, R, Scala</t>
+          <t>RAG, S3, EC2, CI/CD, Git, MySQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5b6f3eb63ee19d0</t>
+          <t>https://www.indeed.com/viewjob?jk=405ba8f351065941</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer - Microsoft Power Platform</t>
+          <t>Agentic Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Rotolo Consultants, Inc. (RCI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Slidell, LA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, CI/CD, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Prompt Engineering, Cortex, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b5a390cb7a511c</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c98bd561aaaf8b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>GCP Cloud Engineer - REMOTE in US</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quanta Infrastructure Solutions Group</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcc30e320d0b67bf</t>
+          <t>https://www.indeed.com/viewjob?jk=fb25af9e8a46ee93</t>
         </is>
       </c>
     </row>
